--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Methods" sheetId="6" r:id="rId6"/>
     <sheet name="Comments" sheetId="7" r:id="rId7"/>
     <sheet name="Documents" sheetId="8" r:id="rId8"/>
+    <sheet name="WhereClauses" sheetId="9" r:id="rId9"/>
+    <sheet name="Standards" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -358,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,36 +390,398 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>StudyName</t>
+          <t>study_oid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDISC01_1</t>
+          <t>STDY.www.cdisc.org.CDISC01_1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>StudyDescription</t>
+          <t>file_oid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDISC Test Study Modified to illustrate Define-XML 2.1 features</t>
+          <t>www.cdisc.org/StudyCDISC01_1/1/Define-XML_2.1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>odm_context</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>metadata_version_oid</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MDV.CDISC01_1.1.SDTMIG.3.1.2.SDTM.1.2_X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>metadata_version_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Study CDISC01_1, Data Definitions V-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>metadata_version_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data Definitions for CDISC01-01 SDTM datasets. This metadata version contains only a subset of datasets compared to the prior version. The metadata provided is only intended to illustrate most Define-XML 2.1 new features and not meant to serve as a comprehensive example of all metadata expected to be defined to fully describe an SDTM dataset package.   Notes:   1) Supplemental documents released in prior Define-XML versions were not updated to reflect changes to the metadata.    2) This example is prepared for a context other than submission; however, still using the approach of non-standard variables prepared as supplemental qualifiers datasets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>originator</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CDISC Data Exchange Standards Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M.Hungria-System</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>source_system_version</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.1-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>StudyName</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CDISC01_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>StudyDescription</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CDISC Test Study Modified to illustrate Define-XML 2.1 features</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>ProtocolName</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CDISC01-1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STD.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SDTMIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COM.STD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STD.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SDTMIG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STD.2_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SDTMIG-MD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.3</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDISC01-1</t>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2011-12-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.CT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STD.4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2015-12-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COM.CT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
         </is>
       </c>
     </row>
@@ -428,7 +792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -472,6 +836,36 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Dataset Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Repeating</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reference Data</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -504,6 +898,31 @@
           <t>SDTMIG 3.1.2</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tabulation</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +960,31 @@
           <t>COM.DOMAIN.DM</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tabulation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,6 +1017,31 @@
           <t>SDTMIG 3.1.2</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tabulation</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,6 +1072,31 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>SDTMIG 3.1.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tabulation</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -613,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -684,27 +1178,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Origin Document</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Predecessor</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Field Name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Has No Data</t>
         </is>
       </c>
     </row>
@@ -729,7 +1238,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F2">
@@ -743,6 +1252,16 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Protocol</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -767,7 +1286,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F3">
@@ -786,6 +1305,16 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
         </is>
       </c>
     </row>
@@ -826,9 +1355,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>MT.TSSEQ</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>TSSEQ</t>
         </is>
       </c>
     </row>
@@ -853,7 +1392,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F5">
@@ -872,6 +1411,16 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
         </is>
       </c>
     </row>
@@ -896,7 +1445,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F6">
@@ -915,6 +1464,16 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>TSPARM</t>
         </is>
       </c>
     </row>
@@ -939,7 +1498,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F7">
@@ -953,6 +1512,16 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Protocol</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>TSVAL</t>
         </is>
       </c>
     </row>
@@ -977,7 +1546,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F8">
@@ -991,6 +1560,16 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>Protocol</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1594,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F9">
@@ -1034,6 +1613,16 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1647,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F10">
@@ -1074,9 +1663,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>MT.USUBJID</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1700,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F11">
@@ -1115,6 +1714,26 @@
       <c r="L11" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SUBJID</t>
         </is>
       </c>
     </row>
@@ -1152,9 +1771,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>MT.RFSTDTC</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>RFSTDTC</t>
         </is>
       </c>
     </row>
@@ -1192,9 +1821,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>MT.RFENDTC</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>RFENDTC</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1858,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F14">
@@ -1233,6 +1872,26 @@
       <c r="L14" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SITEID</t>
         </is>
       </c>
     </row>
@@ -1270,6 +1929,26 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>BRTHDTC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1308,9 +1987,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>MT.AGE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>AGE</t>
         </is>
       </c>
     </row>
@@ -1335,7 +2024,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F17">
@@ -1351,9 +2040,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>COM.AGEU</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>AGEU</t>
         </is>
       </c>
     </row>
@@ -1378,7 +2077,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F18">
@@ -1397,6 +2096,26 @@
       <c r="L18" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>SEX</t>
         </is>
       </c>
     </row>
@@ -1421,7 +2140,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F19">
@@ -1442,14 +2161,34 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>MT.RACE</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>COM.RACE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>RACE</t>
         </is>
       </c>
     </row>
@@ -1474,7 +2213,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F20">
@@ -1493,6 +2232,26 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>ETHNIC</t>
         </is>
       </c>
     </row>
@@ -1517,7 +2276,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F21">
@@ -1538,9 +2297,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>COM.ARMCD</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ARMCD</t>
         </is>
       </c>
     </row>
@@ -1565,7 +2334,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F22">
@@ -1586,9 +2355,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>COM.ARM</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ARM</t>
         </is>
       </c>
     </row>
@@ -1613,7 +2392,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F23">
@@ -1627,6 +2406,16 @@
       <c r="L23" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
         </is>
       </c>
     </row>
@@ -1651,7 +2440,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F24">
@@ -1665,6 +2454,16 @@
       <c r="L24" t="inlineStr">
         <is>
           <t>Protocol</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -1689,7 +2488,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F25">
@@ -1708,6 +2507,16 @@
       <c r="L25" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
         </is>
       </c>
     </row>
@@ -1732,7 +2541,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F26">
@@ -1748,9 +2557,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>MT.USUBJID</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -1791,9 +2610,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>MT.SEQ</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>VSSEQ</t>
         </is>
       </c>
     </row>
@@ -1818,7 +2647,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F28">
@@ -1837,6 +2666,16 @@
       <c r="L28" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
         </is>
       </c>
     </row>
@@ -1861,7 +2700,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F29">
@@ -1880,6 +2719,26 @@
       <c r="L29" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>VSTEST</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2763,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F30">
@@ -1918,6 +2777,26 @@
       <c r="L30" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>VSPOS</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2821,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F31">
@@ -1956,6 +2835,26 @@
       <c r="L31" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>VSORRES</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2879,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F32">
@@ -1994,6 +2893,26 @@
       <c r="L32" t="inlineStr">
         <is>
           <t>Collected</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>VSORRESU</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2937,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F33">
@@ -2034,14 +2953,24 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>MT.VSSTRESC</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>COM.VSSTRESC</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>VSSTRESC</t>
         </is>
       </c>
     </row>
@@ -2090,14 +3019,24 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>MT.VSSTRESN</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>COM.VSSTRESN</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>VSSTRESN</t>
         </is>
       </c>
     </row>
@@ -2122,7 +3061,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F35">
@@ -2143,9 +3082,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>COM.VSSTRESU</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>VSSTRESU</t>
         </is>
       </c>
     </row>
@@ -2170,7 +3119,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F36">
@@ -2191,9 +3140,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>MT.VSBLFL</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>VSBLFL</t>
         </is>
       </c>
     </row>
@@ -2239,9 +3198,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>COM.VS.VISITNUM</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>VISITNUM</t>
         </is>
       </c>
     </row>
@@ -2266,7 +3235,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F38">
@@ -2280,6 +3249,16 @@
       <c r="L38" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>VISIT</t>
         </is>
       </c>
     </row>
@@ -2320,6 +3299,16 @@
           <t>Protocol</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>VISITDY</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2355,6 +3344,26 @@
           <t>Collected</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>VSDTC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2393,9 +3402,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>MT.VSDY</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>VSDY</t>
         </is>
       </c>
     </row>
@@ -2420,7 +3439,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F42">
@@ -2434,6 +3453,16 @@
       <c r="L42" t="inlineStr">
         <is>
           <t>Protocol</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
         </is>
       </c>
     </row>
@@ -2458,7 +3487,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F43">
@@ -2474,9 +3503,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>MT.RDOMAIN</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>RDOMAIN</t>
         </is>
       </c>
     </row>
@@ -2501,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F44">
@@ -2517,9 +3556,19 @@
           <t>Derived</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>MT.USUBJID</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
         </is>
       </c>
     </row>
@@ -2544,7 +3593,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F45">
@@ -2560,9 +3609,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>COM.IDVAR</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>IDVAR</t>
         </is>
       </c>
     </row>
@@ -2587,7 +3646,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F46">
@@ -2603,9 +3662,19 @@
           <t>Assigned</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>COM.IDVARVAL</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>IDVARVAL</t>
         </is>
       </c>
     </row>
@@ -2630,7 +3699,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F47">
@@ -2644,6 +3713,16 @@
       <c r="L47" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>QNAM</t>
         </is>
       </c>
     </row>
@@ -2668,7 +3747,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F48">
@@ -2682,6 +3761,16 @@
       <c r="L48" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>QLABEL</t>
         </is>
       </c>
     </row>
@@ -2706,7 +3795,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F49">
@@ -2715,6 +3804,11 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>QVAL</t>
         </is>
       </c>
     </row>
@@ -2739,7 +3833,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F50">
@@ -2753,6 +3847,16 @@
       <c r="L50" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>QORIG</t>
         </is>
       </c>
     </row>
@@ -2777,7 +3881,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F51">
@@ -2791,6 +3895,16 @@
       <c r="L51" t="inlineStr">
         <is>
           <t>Assigned</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>QEVAL</t>
         </is>
       </c>
     </row>
@@ -2815,7 +3929,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -2851,7 +3965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2892,17 +4006,97 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Significant Digits</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Codelist</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Method</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>where_clause_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>itemoid</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sas_field_name</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>origin_description</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>origin_document_id</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>page_type</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>page_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>value_list_id</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>predecessor</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>assigned_value</t>
         </is>
       </c>
     </row>
@@ -2938,19 +4132,59 @@
       <c r="G2">
         <v>41</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CL.RACE</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>MT.RACE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.RACE1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>RACE1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -2986,19 +4220,59 @@
       <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>CL.RACE</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>MT.RACE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.RACE2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>RACE2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3034,19 +4308,59 @@
       <c r="G4">
         <v>41</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>CL.RACE</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>MT.RACE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.RACE3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>RACE3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3082,14 +4396,54 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>CL.NY</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RAND</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.RAND</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>RAND</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3125,9 +4479,49 @@
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RANDNO</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.RANDNO</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RANDNO</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3163,19 +4557,44 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>CL.NY</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>MT.SAFETY</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.SAFETY</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>IT.SUPPDM.QVAL.SAFETY</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3211,9 +4630,34 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMAX</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.AGEMAX</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>AGEMAX</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3249,9 +4693,34 @@
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMIN</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.AGEMIN</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>AGEMIN</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3287,14 +4756,39 @@
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>CL.AGEU</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEU</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.AGEU</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>AGEU</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3330,9 +4824,34 @@
       <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.DOSE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.DOSE</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3368,14 +4887,39 @@
       <c r="G12">
         <v>3</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>CL.COUNTRY.STUDY</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.FCNTRY</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.FCNTRY</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>FCNTRY</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3411,9 +4955,34 @@
       <c r="G13">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.PLANSUB</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>IT.TS.TSVAL.PLANSUB</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>PLANSUB</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -3449,9 +5018,49 @@
       <c r="G14">
         <v>2</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.DIABP</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.DIABP</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>DIABPOR</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3487,14 +5096,54 @@
       <c r="G15">
         <v>6</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>CL.SIZE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>FRMSZOR</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3530,9 +5179,57 @@
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.HEIGHT</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>HEIGHTOR</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3568,9 +5265,49 @@
       <c r="G17">
         <v>2</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.PULSE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.PULSE</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>PULSEOR</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3606,9 +5343,49 @@
       <c r="G18">
         <v>3</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.SYSBP</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>SYSBPOR</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3644,9 +5421,57 @@
       <c r="G19">
         <v>4</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRES.WEIGHT</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>WEIGHTOR</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -3682,9 +5507,24 @@
       <c r="G20">
         <v>2</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.DIABP</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.DIABP</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>DIABPSC</t>
         </is>
       </c>
     </row>
@@ -3720,14 +5560,29 @@
       <c r="G21">
         <v>6</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>CL.SIZE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>FRMSZSC</t>
         </is>
       </c>
     </row>
@@ -3763,9 +5618,32 @@
       <c r="G22">
         <v>5</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.HEIGHT</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>HEIGHTSC</t>
         </is>
       </c>
     </row>
@@ -3801,9 +5679,24 @@
       <c r="G23">
         <v>2</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.PULSE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.PULSE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>PULSESC</t>
         </is>
       </c>
     </row>
@@ -3839,9 +5732,24 @@
       <c r="G24">
         <v>3</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.SYSBP</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>SYSBPSC</t>
         </is>
       </c>
     </row>
@@ -3877,9 +5785,32 @@
       <c r="G25">
         <v>4</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.WEIGHT</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>WEIGHTSC</t>
         </is>
       </c>
     </row>
@@ -3915,14 +5846,37 @@
       <c r="G26">
         <v>6</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>MT.BMISC</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.BMI</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESC.BMI</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>BMISC</t>
         </is>
       </c>
     </row>
@@ -3958,9 +5912,24 @@
       <c r="G27">
         <v>2</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.DIABP</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.DIABP</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>DIABPSN</t>
         </is>
       </c>
     </row>
@@ -3996,9 +5965,32 @@
       <c r="G28">
         <v>5</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.HEIGHT</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>HEIGHTSN</t>
         </is>
       </c>
     </row>
@@ -4034,9 +6026,24 @@
       <c r="G29">
         <v>2</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.PULSE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.PULSE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>PULSESN</t>
         </is>
       </c>
     </row>
@@ -4072,9 +6079,24 @@
       <c r="G30">
         <v>3</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.SYSBP</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>SYSBPSN</t>
         </is>
       </c>
     </row>
@@ -4110,9 +6132,32 @@
       <c r="G31">
         <v>4</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.WEIGHT</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>WEIGHTSN</t>
         </is>
       </c>
     </row>
@@ -4148,14 +6193,67 @@
       <c r="G32">
         <v>6</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>MT.BMISN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.BMI</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>IT.VS.VSSTRESN.BMI</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>BMISN</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>EDC System</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -4191,14 +6289,59 @@
       <c r="G33">
         <v>5</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>CL.UH_MC</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>COM.STUDY.DATA</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRESU.HEIGHT.DM.COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>HEIGHTOM</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -4234,14 +6377,54 @@
       <c r="G34">
         <v>5</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>CL.UH_NMC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRESU.HEIGHT.DM.COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>HEIGHTON</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -4277,14 +6460,59 @@
       <c r="G35">
         <v>4</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>CL.UW_MC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>COM.STUDY.DATA</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRESU.WEIGHT.DM.COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>WEIGHTOM</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -4320,14 +6548,54 @@
       <c r="G36">
         <v>4</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>CL.UW_NMC</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>IT.VS.VSORRESU.WEIGHT.DM.COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>WEIGHTON</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Investigator</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -4338,7 +6606,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4362,6 +6630,36 @@
           <t>Decoded Value</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Codelist Code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SAS Format Name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>NCI Term Code</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4377,6 +6675,26 @@
           <t>YEARS</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Age Unit</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>C66781</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C29848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4389,6 +6707,16 @@
           <t>Miracle Drug 10 mg</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Description of Planned Arm</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4401,6 +6729,16 @@
           <t>Miracle Drug 20 mg</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Description of Planned Arm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4413,6 +6751,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Description of Planned Arm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4425,6 +6773,16 @@
           <t>Screen Failure</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Description of Planned Arm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4445,6 +6803,21 @@
           <t>Miracle Drug 10 mg</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Planned Arm Code</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$ARMCD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4465,6 +6838,21 @@
           <t>Miracle Drug 20 mg</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Planned Arm Code</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$ARMCD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4485,6 +6873,21 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Planned Arm Code</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$ARMCD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4505,6 +6908,21 @@
           <t>Screen Failure</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Planned Arm Code</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$ARMCD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4522,6 +6940,21 @@
           <t>United States of America (the)</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Study Planned Countries</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4539,6 +6972,21 @@
           <t>Canada</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Study Planned Countries</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4556,6 +7004,21 @@
           <t>Mexico</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Study Planned Countries</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4573,6 +7036,31 @@
           <t>Device Identifiers</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (DI)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$DIDOMAI</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C102618</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4590,6 +7078,31 @@
           <t>Demographics</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (DM)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$DMDOMAI</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C49572</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4607,6 +7120,31 @@
           <t>Exposure as Collected</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (EC)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$ECDOMAI</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>C49587</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4619,6 +7157,26 @@
           <t>HISPANIC OR LATINO</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C17459</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4631,6 +7189,26 @@
           <t>NOT HISPANIC OR LATINO</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ethnic Group</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C66790</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C41222</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4648,6 +7226,31 @@
           <t>Exposure</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (EX)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$EXDOMAI</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C49587</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4660,6 +7263,16 @@
           <t>Miracle Drug</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4672,6 +7285,16 @@
           <t>Placebo</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4689,6 +7312,31 @@
           <t>tab</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Dosage Form</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>C66726</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>$FRM</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C42998</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4706,6 +7354,31 @@
           <t>Laboratory Data</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (LB)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>$LBDOMAI</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C49592</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4723,6 +7396,31 @@
           <t>Percentage</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4740,6 +7438,26 @@
           <t>X10^9/L</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4757,6 +7475,31 @@
           <t>Gram per Deciliter</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C64783</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4774,6 +7517,31 @@
           <t>Milligram per Deciliter</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C67015</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4791,6 +7559,31 @@
           <t>Nanogram per Deciliter</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C67326</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4808,6 +7601,26 @@
           <t>pg/mL</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Unit (LBRESU)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$LBRESU</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4820,6 +7633,26 @@
           <t>Bilirubin</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C38037</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4832,6 +7665,26 @@
           <t>Blood Urea Nitrogen</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C61019</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4844,6 +7697,26 @@
           <t>Glucose</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C41376</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4856,6 +7729,26 @@
           <t>Hematocrit</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C64796</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4868,6 +7761,26 @@
           <t>Hemoglobin</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C64848</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4880,6 +7793,26 @@
           <t>Lymphocytes</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C51949</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4892,6 +7825,26 @@
           <t>Occult Blood</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C74686</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4904,6 +7857,26 @@
           <t>Vitamin B12</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C64817</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4916,6 +7889,26 @@
           <t>Vitamin B9</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C74676</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4928,6 +7921,26 @@
           <t>pH</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Laboratory Test Name</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>C67154</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C45997</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4945,6 +7958,31 @@
           <t>Bilirubin</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C38037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4962,6 +8000,31 @@
           <t>Blood Urea Nitrogen</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C61019</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4979,6 +8042,31 @@
           <t>Glucose</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C41376</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4996,6 +8084,31 @@
           <t>Hematocrit</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C64796</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5013,6 +8126,31 @@
           <t>Hemoglobin</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C64848</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5030,6 +8168,31 @@
           <t>Lymphocytes</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C51949</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5047,6 +8210,31 @@
           <t>Occult Blood</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C74686</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5064,6 +8252,31 @@
           <t>pH</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C45997</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5081,6 +8294,31 @@
           <t>Vitamin B12</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C64817</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5098,6 +8336,31 @@
           <t>Vitamin B9</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Laboratory Test Code</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>C65047</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>$LBTESTC</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C74676</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5110,6 +8373,21 @@
           <t>DIPSTICK</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>C85492</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5122,6 +8400,21 @@
           <t>QUANT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>C85492</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5134,6 +8427,26 @@
           <t>ABNORMAL</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Reference Range Indicator</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>C78736</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C78802</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5146,6 +8459,26 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Reference Range Indicator</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>C78736</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>C78800</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5158,6 +8491,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Reference Range Indicator</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C78736</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>C78801</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5170,6 +8523,26 @@
           <t>NORMAL</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Reference Range Indicator</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C78736</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C78727</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5187,6 +8560,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No Yes Response Subset</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>$NY</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C49488</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5204,6 +8602,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No Yes Response Subset</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>$NY</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C49487</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5221,6 +8644,31 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No Yes Response Subset</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>$NY</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C17998</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5236,6 +8684,26 @@
           <t>WHITE</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C41261</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5251,6 +8719,26 @@
           <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C41259</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5266,6 +8754,26 @@
           <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C16352</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5281,6 +8789,26 @@
           <t>ASIAN</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C41260</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5296,6 +8824,26 @@
           <t>NATIVE HAWAIIAN OR OTHER PACIFIC ISLANDER</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>C41219</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5313,6 +8861,31 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>$SEX</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C16576</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5330,6 +8903,31 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>$SEX</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C20197</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5347,6 +8945,31 @@
           <t>Unknown</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>$SEX</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C17998</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5364,6 +8987,31 @@
           <t>Undifferentiated</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>C66731</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>$SEX</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C17998</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5376,6 +9024,29 @@
           <t>SMALL</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>C66733</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>C25376</t>
+        </is>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5388,6 +9059,29 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>C66733</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>C49507</t>
+        </is>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5400,6 +9094,29 @@
           <t>LARGE</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>C66733</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C49508</t>
+        </is>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5412,6 +9129,26 @@
           <t>BLOOD</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Specimen Type</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>C78734</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>C12434</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5424,6 +9161,26 @@
           <t>SERUM</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Specimen Type</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>C78734</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C13325</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5436,6 +9193,26 @@
           <t>URINE</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Specimen Type</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>C78734</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>C13283</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5453,6 +9230,31 @@
           <t>Trial Summary</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (TS)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>$TSDOMAI</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>C53483</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5465,6 +9267,26 @@
           <t>Added on to Existing Treatments</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>C49703</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5477,6 +9299,26 @@
           <t>Age Span</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>C20587</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5489,6 +9331,21 @@
           <t>Age Unit</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5501,6 +9358,26 @@
           <t>Clinical Study Sponsor</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>C70793</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5513,6 +9390,26 @@
           <t>Control Type</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>C49647</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5525,6 +9422,26 @@
           <t>Dose Units</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>C73558</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5537,6 +9454,26 @@
           <t>Dose per Administration</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>C25488</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5549,6 +9486,26 @@
           <t>Dosing Frequency</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>C89081</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5561,6 +9518,26 @@
           <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>C41161</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5573,6 +9550,26 @@
           <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>C98770</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5585,6 +9582,26 @@
           <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>C49694</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5597,6 +9614,26 @@
           <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>C49693</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5609,6 +9646,26 @@
           <t>Planned Number of Subjects</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>C49692</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5621,6 +9678,26 @@
           <t>Route of Administration</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>C38114</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5633,6 +9710,26 @@
           <t>Sex of Participants</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>C49696</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5645,6 +9742,26 @@
           <t>Trial Blinding Schema</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>C49658</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5657,6 +9774,26 @@
           <t>Trial Indication Type</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>C49652</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5669,6 +9806,26 @@
           <t>Trial Length</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>C49697</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5681,6 +9838,26 @@
           <t>Trial Phase Classification</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>C48281</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5693,6 +9870,26 @@
           <t>Trial Primary Objective</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>C85826</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5705,6 +9902,26 @@
           <t>Trial Secondary Objective</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>C85827</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5717,6 +9934,26 @@
           <t>Trial Title</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>C49802</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5729,6 +9966,26 @@
           <t>Trial Type</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>C49660</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5741,6 +9998,26 @@
           <t>Trial is Randomized</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Name</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>C25196</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5758,6 +10035,31 @@
           <t>Added on to Existing Treatments</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>C49703</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5775,6 +10077,31 @@
           <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>C49694</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5792,6 +10119,31 @@
           <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>C49693</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5809,6 +10161,31 @@
           <t>Age Span</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>C20587</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5826,6 +10203,26 @@
           <t>Age Unit</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5843,6 +10240,31 @@
           <t>Dose per Administration</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>C25488</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5860,6 +10282,31 @@
           <t>Dosing Frequency</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>C89081</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5877,6 +10324,31 @@
           <t>Dose Units</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>C73558</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5894,6 +10366,31 @@
           <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>C98770</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5911,6 +10408,31 @@
           <t>Trial Length</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>C49697</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5928,6 +10450,31 @@
           <t>Trial Primary Objective</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>C85826</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5945,6 +10492,31 @@
           <t>Trial Secondary Objective</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>C85827</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5962,6 +10534,31 @@
           <t>Planned Number of Subjects</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>C49692</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5979,6 +10576,31 @@
           <t>Trial is Randomized</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>C25196</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5996,6 +10618,31 @@
           <t>Route of Administration</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>C38114</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6013,6 +10660,31 @@
           <t>Sex of Participants</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>C49696</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6030,6 +10702,31 @@
           <t>Clinical Study Sponsor</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>C70793</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6047,6 +10744,31 @@
           <t>Trial Blinding Schema</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>C49658</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6064,6 +10786,31 @@
           <t>Control Type</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>C49647</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6081,6 +10828,31 @@
           <t>Trial Indication Type</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>C49652</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6098,6 +10870,31 @@
           <t>Trial Title</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>C49802</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6115,6 +10912,31 @@
           <t>Trial Phase Classification</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>C48281</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6132,6 +10954,31 @@
           <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>C41161</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6149,6 +10996,31 @@
           <t>Trial Type</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Trial Summary Parameter Test Code</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>C49660</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6166,6 +11038,31 @@
           <t>Centimeter</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Unit (UH_MC)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>$UH_MC</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>C49668</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6183,6 +11080,31 @@
           <t>Inch</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Unit (UH_NMC)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>$UH_NMC</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>C48500</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6200,6 +11122,31 @@
           <t>Kilogram</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Unit (UW_MC)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>$UW_MC</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6217,6 +11164,31 @@
           <t>Pound</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Unit (UW_NMC)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>$UW_NMC</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>C48531</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6234,6 +11206,31 @@
           <t>Vital Signs</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation (VS)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>$VSDOMAI</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>C49622</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6251,6 +11248,31 @@
           <t>Beats per Minute</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Units for Vital Signs Orig Results</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>C49673</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6268,6 +11290,31 @@
           <t>Centimeter</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Units for Vital Signs Orig Results</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>C49668</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6285,6 +11332,31 @@
           <t>Kilogram</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Units for Vital Signs Orig Results</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>C28252</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6302,6 +11374,31 @@
           <t>Millimeter of Mercury</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Units for Vital Signs Orig Results</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>C49670</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6319,6 +11416,31 @@
           <t>Kilogram per Square Meter</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Units for Vital Signs Orig Results</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>C49671</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6331,6 +11453,26 @@
           <t>Body Mass Index</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>C16358</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6343,6 +11485,26 @@
           <t>Body Frame Size</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>C49680</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6355,6 +11517,26 @@
           <t>Diastolic Blood Pressure</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>C25299</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6367,6 +11549,26 @@
           <t>Height</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>C25347</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6379,6 +11581,26 @@
           <t>Pulse Rate</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>C49676</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6391,6 +11613,26 @@
           <t>Systolic Blood Pressure</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>C25298</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6403,6 +11645,26 @@
           <t>Weight</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Name</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>C25208</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6420,6 +11682,31 @@
           <t>Body Mass Index</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>C16358</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6437,6 +11724,31 @@
           <t>Diastolic Blood Pressure</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>C25299</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6454,6 +11766,31 @@
           <t>Body Frame Size</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>C49680</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6471,6 +11808,31 @@
           <t>Height</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>C25347</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6488,6 +11850,31 @@
           <t>Pulse Rate</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>C49676</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6505,6 +11892,31 @@
           <t>Systolic Blood Pressure</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>C25298</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6522,6 +11934,31 @@
           <t>Weight</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Vital Signs Test Code</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>C25208</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6539,6 +11976,26 @@
           <t>g/dL</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Units for S Findings Results</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>$XSRESU</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>C64783</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6556,6 +12013,26 @@
           <t>mg/dL</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Units for S Findings Results</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>$XSRESU</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>C67015</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6568,6 +12045,16 @@
           <t>Test 1</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>S Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6580,6 +12067,16 @@
           <t>Test 2</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>S Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6592,6 +12089,16 @@
           <t>Test 3</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>S Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6609,6 +12116,21 @@
           <t>Test 1</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>S Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>$XSTESTC</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6626,6 +12148,21 @@
           <t>Test 2</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>S Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>$XSTESTC</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6643,6 +12180,21 @@
           <t>Test 3</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>S Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>$XSTESTC</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6660,6 +12212,26 @@
           <t>g/dL</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Units for X Findings Results</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>$XXRESU</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>C64783</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6677,6 +12249,26 @@
           <t>mg/dL</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Units for X Findings Results</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>$XXRESU</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>C67015</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6694,6 +12286,26 @@
           <t>%</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Units for X Findings Results</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>$XXRESU</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>C25613</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6706,6 +12318,16 @@
           <t>Test 11</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>X Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6718,6 +12340,16 @@
           <t>Test 12</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>X Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6730,6 +12362,16 @@
           <t>Test 13</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>X Findings Test Name</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6747,6 +12389,21 @@
           <t>Test 11</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>X Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>$XXTESTC</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6764,6 +12421,21 @@
           <t>Test 12</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>X Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>$XXTESTC</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6779,6 +12451,21 @@
       <c r="D163" t="inlineStr">
         <is>
           <t>Test 13</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>X Findings Test Code</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>$XXTESTC</t>
         </is>
       </c>
     </row>
@@ -8003,7 +13690,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8022,6 +13709,11 @@
           <t>Href</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8039,6 +13731,11 @@
           <t>ts.xpt</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8056,6 +13753,11 @@
           <t>di.xpt</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8073,6 +13775,11 @@
           <t>dm.xpt</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8090,6 +13797,11 @@
           <t>ec.xpt</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8107,6 +13819,11 @@
           <t>ex.xpt</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8124,6 +13841,11 @@
           <t>lb.xpt</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8141,6 +13863,11 @@
           <t>vs.xpt</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8158,6 +13885,11 @@
           <t>xs.xpt</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8175,6 +13907,11 @@
           <t>suppdm.xpt</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8192,6 +13929,11 @@
           <t>acrf.pdf</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8209,6 +13951,11 @@
           <t>csdrg.pdf</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>supplemental</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8224,6 +13971,822 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>complexalgorithms.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>supplemental</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comparator</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RACE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RACE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RACE3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RACE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RAND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.RANDNO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RANDNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WC.SUPPDM.QNAM.SAFETY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUPPDM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>QNAM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMAX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AGEMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMIN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AGEMIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AGEU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.DOSE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.FCNTRY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FCNTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.PLANSUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PLANSUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.BMI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.DIABP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIABP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FRMSIZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(CAN, MEX)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.PULSE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SYSBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(CAN, MEX)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QNAM EQ (RACE1)</t>
+          <t>WC.SUPPDM.QNAM.RACE1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QNAM EQ (RACE2)</t>
+          <t>WC.SUPPDM.QNAM.RACE2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>QNAM EQ (RACE3)</t>
+          <t>WC.SUPPDM.QNAM.RACE3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QNAM EQ (RAND)</t>
+          <t>WC.SUPPDM.QNAM.RAND</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QNAM EQ (RANDNO)</t>
+          <t>WC.SUPPDM.QNAM.RANDNO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>QNAM EQ (SAFETY)</t>
+          <t>WC.SUPPDM.QNAM.SAFETY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (AGEMAX)</t>
+          <t>WC.TS.TSPARMCD.AGEMAX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (AGEMIN)</t>
+          <t>WC.TS.TSPARMCD.AGEMIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (AGEU)</t>
+          <t>WC.TS.TSPARMCD.AGEU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (DOSE)</t>
+          <t>WC.TS.TSPARMCD.DOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (FCNTRY)</t>
+          <t>WC.TS.TSPARMCD.FCNTRY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ (PLANSUB)</t>
+          <t>WC.TS.TSPARMCD.PLANSUB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (DIABP)</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (FRMSIZE)</t>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (HEIGHT)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (PULSE)</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (SYSBP)</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (WEIGHT)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (DIABP)</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (FRMSIZE)</t>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (HEIGHT)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (PULSE)</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (SYSBP)</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (WEIGHT)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (BMI)</t>
+          <t>WC.VS.VSTESTCD.BMI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (DIABP)</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (HEIGHT)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (PULSE)</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (SYSBP)</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (WEIGHT)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (BMI)</t>
+          <t>WC.VS.VSTESTCD.BMI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (HEIGHT) AND COUNTRY IN (CAN, MEX)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (HEIGHT) AND COUNTRY EQ (USA)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (WEIGHT) AND COUNTRY IN (CAN, MEX)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ (WEIGHT) AND COUNTRY EQ (USA)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -3965,7 +3965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4086,15 +4086,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>role_codelist_id</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>value_list_id</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>predecessor</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>assigned_value</t>
         </is>
@@ -4187,6 +4197,11 @@
           <t>PhysicalRef</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -4275,6 +4290,11 @@
           <t>PhysicalRef</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -4363,6 +4383,11 @@
           <t>PhysicalRef</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -4446,6 +4471,11 @@
           <t>PhysicalRef</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -4524,6 +4554,11 @@
           <t>PhysicalRef</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -4595,6 +4630,11 @@
       <c r="R7" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6646,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7023,22 +7063,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CL.DI.DOMAIN</t>
+          <t>CL.DM.DOMAIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Device Identifiers</t>
+          <t>Demographics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (DI)</t>
+          <t>Domain Abbreviation (DM)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7053,34 +7093,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$DIDOMAI</t>
+          <t>$DMDOMAI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C102618</t>
+          <t>C49572</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CL.DM.DOMAIN</t>
+          <t>CL.ETHNIC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Demographics</t>
+          <t>HISPANIC OR LATINO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (DM)</t>
+          <t>Ethnic Group</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -7090,39 +7125,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C66734</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>$DMDOMAI</t>
+          <t>C66790</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C49572</t>
+          <t>C17459</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CL.EC.DOMAIN</t>
+          <t>CL.ETHNIC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Exposure as Collected</t>
+          <t>NOT HISPANIC OR LATINO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (EC)</t>
+          <t>Ethnic Group</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7132,34 +7157,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C66734</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>$ECDOMAI</t>
+          <t>C66790</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C49587</t>
+          <t>C41222</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.NY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HISPANIC OR LATINO</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnic Group</t>
+          <t>No Yes Response Subset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7169,29 +7194,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C66790</t>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$NY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C17459</t>
+          <t>C49488</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CL.ETHNIC</t>
+          <t>CL.NY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOT HISPANIC OR LATINO</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethnic Group</t>
+          <t>No Yes Response Subset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7201,34 +7236,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C66790</t>
+          <t>C66742</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$NY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C41222</t>
+          <t>C49487</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CL.EX.DOMAIN</t>
+          <t>CL.NY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Exposure</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (EX)</t>
+          <t>No Yes Response Subset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7238,83 +7278,107 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C66734</t>
+          <t>C66742</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$EXDOMAI</t>
+          <t>$NY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C49587</t>
+          <t>C17998</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CL.EXTRT</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miracle Drug</t>
+          <t>WHITE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C41261</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CL.EXTRT</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>text</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>C74457</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>C41259</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CL.FRM</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TABLET</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>tab</t>
+          <t>BLACK OR AFRICAN AMERICAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pharmaceutical Dosage Form</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7324,39 +7388,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C66726</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>$FRM</t>
+          <t>C74457</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C42998</t>
+          <t>C16352</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CL.LB.DOMAIN</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Laboratory Data</t>
+          <t>ASIAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (LB)</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7366,39 +7423,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C66734</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>$LBDOMAI</t>
+          <t>C74457</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C49592</t>
+          <t>C41260</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
-        </is>
+          <t>CL.RACE</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Percentage</t>
+          <t>NATIVE HAWAIIAN OR OTHER PACIFIC ISLANDER</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Race</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7408,39 +7458,34 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>$LBRESU</t>
+          <t>C74457</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C25613</t>
+          <t>C41219</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>X10^9/L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>X10^9/L</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7450,34 +7495,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$LBRESU</t>
+          <t>$SEX</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>C16576</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>g/dL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gram per Deciliter</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7487,39 +7537,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>$LBRESU</t>
+          <t>$SEX</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C64783</t>
+          <t>C20197</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Milligram per Deciliter</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7529,39 +7579,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>$LBRESU</t>
+          <t>$SEX</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C67015</t>
+          <t>C17998</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
+          <t>CL.SEX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ng/dL</t>
+          <t>UNDIFFERENTIATED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nanogram per Deciliter</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -7571,39 +7621,34 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>$LBRESU</t>
+          <t>$SEX</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C67326</t>
+          <t>C17998</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CL.LBRESU</t>
+          <t>CL.SIZE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pg/mL</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>pg/mL</t>
+          <t>SMALL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unit (LBRESU)</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7613,29 +7658,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>$LBRESU</t>
-        </is>
+          <t>C66733</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C25376</t>
+        </is>
+      </c>
+      <c r="J29">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.SIZE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bilirubin</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -7645,29 +7693,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C66733</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C38037</t>
-        </is>
+          <t>C49507</t>
+        </is>
+      </c>
+      <c r="J30">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.SIZE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Blood Urea Nitrogen</t>
+          <t>LARGE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -7677,29 +7728,37 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C66733</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C61019</t>
-        </is>
+          <t>C49508</t>
+        </is>
+      </c>
+      <c r="J31">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TS.DOMAIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glucose</t>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Trial Summary</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Domain Abbreviation (TS)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7709,29 +7768,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$TSDOMAI</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C41376</t>
+          <t>C53483</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hematocrit</t>
+          <t>Added on to Existing Treatments</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -7741,29 +7805,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C64796</t>
+          <t>C49703</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hemoglobin</t>
+          <t>Age Span</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -7773,29 +7837,29 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C64848</t>
+          <t>C20587</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lymphocytes</t>
+          <t>Age Unit</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7805,29 +7869,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C67154</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>C51949</t>
+          <t>C67152</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Occult Blood</t>
+          <t>Clinical Study Sponsor</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7837,29 +7896,29 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C74686</t>
+          <t>C70793</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vitamin B12</t>
+          <t>Control Type</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7869,29 +7928,29 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C64817</t>
+          <t>C49647</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vitamin B9</t>
+          <t>Dose Units</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7901,29 +7960,29 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C74676</t>
+          <t>C73558</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CL.LBTEST</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Dose per Administration</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Laboratory Test Name</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7933,34 +7992,29 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C45997</t>
+          <t>C25488</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BILI</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Bilirubin</t>
+          <t>Dosing Frequency</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7970,39 +8024,29 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C38037</t>
+          <t>C89081</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BUN</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Blood Urea Nitrogen</t>
+          <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8012,39 +8056,29 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C61019</t>
+          <t>C41161</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GLUC</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Glucose</t>
+          <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8054,39 +8088,29 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C41376</t>
+          <t>C98770</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HCT</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Hematocrit</t>
+          <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8096,39 +8120,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C64796</t>
+          <t>C49694</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HGB</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Hemoglobin</t>
+          <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8138,39 +8152,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C64848</t>
+          <t>C49693</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LYM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Lymphocytes</t>
+          <t>Planned Number of Subjects</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8180,39 +8184,29 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C51949</t>
+          <t>C49692</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OCCBLD</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Occult Blood</t>
+          <t>Route of Administration</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8222,39 +8216,29 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C74686</t>
+          <t>C38114</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>pH</t>
+          <t>Sex of Participants</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8264,39 +8248,29 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C45997</t>
+          <t>C49696</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VITB12</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Vitamin B12</t>
+          <t>Trial Blinding Schema</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8306,39 +8280,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C64817</t>
+          <t>C49658</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CL.LBTESTCD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VITB9</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Vitamin B9</t>
+          <t>Trial Indication Type</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Laboratory Test Code</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -8348,34 +8312,29 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C65047</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>$LBTESTC</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C74676</t>
+          <t>C49652</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CL.METHOD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIPSTICK</t>
+          <t>Trial Length</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -8385,24 +8344,29 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C85492</t>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C49697</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CL.METHOD</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QUANT</t>
+          <t>Trial Phase Classification</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8412,24 +8376,29 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C85492</t>
+          <t>C67152</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>C48281</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CL.NRIND</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ABNORMAL</t>
+          <t>Trial Primary Objective</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reference Range Indicator</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8439,29 +8408,29 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C78736</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C78802</t>
+          <t>C85826</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CL.NRIND</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Trial Secondary Objective</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Reference Range Indicator</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -8471,29 +8440,29 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C78736</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C78800</t>
+          <t>C85827</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CL.NRIND</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Trial Title</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Reference Range Indicator</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -8503,29 +8472,29 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C78736</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C78801</t>
+          <t>C49802</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CL.NRIND</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>Trial Type</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reference Range Indicator</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -8535,34 +8504,29 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C78736</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C78727</t>
+          <t>C49660</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CL.NY</t>
+          <t>CL.TSPARM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Trial is Randomized</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No Yes Response Subset</t>
+          <t>Trial Summary Parameter Test Name</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -8572,39 +8536,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C66742</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>$NY</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C49488</t>
+          <t>C25196</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CL.NY</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADDON</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Added on to Existing Treatments</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No Yes Response Subset</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -8614,39 +8573,39 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C66742</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>$NY</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C49487</t>
+          <t>C49703</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CL.NY</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>AGEMAX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No Yes Response Subset</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8656,37 +8615,39 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C66742</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>$NY</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C17998</t>
+          <t>C49694</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>1</v>
+          <t>CL.TSPARMCD</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WHITE</t>
+          <t>AGEMIN</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -8696,32 +8657,39 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C74457</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C41261</t>
+          <t>C49693</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>2</v>
+          <t>CL.TSPARMCD</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AMERICAN INDIAN OR ALASKA NATIVE</t>
+          <t>AGESPAN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Age Span</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8731,32 +8699,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C74457</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C41259</t>
+          <t>C20587</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>3</v>
+          <t>CL.TSPARMCD</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BLACK OR AFRICAN AMERICAN</t>
+          <t>AGEU</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Age Unit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8766,32 +8741,34 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C74457</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C16352</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>4</v>
+          <t>CL.TSPARMCD</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ASIAN</t>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Dose per Administration</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8801,32 +8778,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C74457</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C41260</t>
+          <t>C25488</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CL.RACE</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>5</v>
+          <t>CL.TSPARMCD</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NATIVE HAWAIIAN OR OTHER PACIFIC ISLANDER</t>
+          <t>DOSFRQ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dosing Frequency</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8836,34 +8820,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C74457</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C41219</t>
+          <t>C89081</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CL.SEX</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>DOSU</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Dose Units</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8873,39 +8862,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C66731</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>$SEX</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C16576</t>
+          <t>C73558</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CL.SEX</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>FCNTRY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8915,39 +8904,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C66731</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>$SEX</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C20197</t>
+          <t>C98770</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CL.SEX</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Trial Length</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8957,39 +8946,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C66731</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>$SEX</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C17998</t>
+          <t>C49697</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CL.SEX</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UNDIFFERENTIATED</t>
+          <t>OBJPRIM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>Trial Primary Objective</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -8999,34 +8988,39 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C66731</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>$SEX</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C17998</t>
+          <t>C85826</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CL.SIZE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SMALL</t>
+          <t>OBJSEC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Trial Secondary Objective</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9036,32 +9030,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C66733</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C25376</t>
-        </is>
-      </c>
-      <c r="J68">
-        <v>1</v>
+          <t>C85827</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CL.SIZE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>PLANSUB</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Planned Number of Subjects</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9071,32 +9072,39 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C66733</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C49507</t>
-        </is>
-      </c>
-      <c r="J69">
-        <v>2</v>
+          <t>C49692</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CL.SIZE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LARGE</t>
+          <t>RANDOM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Trial is Randomized</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9106,32 +9114,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C66733</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C49508</t>
-        </is>
-      </c>
-      <c r="J70">
-        <v>3</v>
+          <t>C25196</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CL.SPECTYPE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BLOOD</t>
+          <t>ROUTE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Route of Administration</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9141,29 +9156,39 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C78734</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C12434</t>
+          <t>C38114</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CL.SPECTYPE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SERUM</t>
+          <t>SEXPOP</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sex of Participants</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9173,29 +9198,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C78734</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>C13325</t>
+          <t>C49696</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CL.SPECTYPE</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>URINE</t>
+          <t>SPONSOR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Clinical Study Sponsor</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Specimen Type</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9205,34 +9240,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C78734</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>C13283</t>
+          <t>C70793</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CL.TS.DOMAIN</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>TBLIND</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Trial Summary</t>
+          <t>Trial Blinding Schema</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Domain Abbreviation (TS)</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9242,34 +9282,39 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C66734</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>$TSDOMAI</t>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>C53483</t>
+          <t>C49658</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Added on to Existing Treatments</t>
+          <t>TCNTRL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Control Type</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9279,29 +9324,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>C49703</t>
+          <t>C49647</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Age Span</t>
+          <t>TINDTP</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Trial Indication Type</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9311,29 +9366,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C20587</t>
+          <t>C49652</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Age Unit</t>
+          <t>TITLE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Trial Title</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9343,24 +9408,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>C49802</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Clinical Study Sponsor</t>
+          <t>TPHASE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Trial Phase Classification</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9370,29 +9450,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C70793</t>
+          <t>C48281</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Control Type</t>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9402,29 +9492,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>C49647</t>
+          <t>C41161</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.TSPARMCD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dose Units</t>
+          <t>TTYPE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Trial Type</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Trial Summary Parameter Test Code</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9434,29 +9534,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66738</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>$TSPARMC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>C73558</t>
+          <t>C49660</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.UH_MC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dose per Administration</t>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Centimeter</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Unit (UH_MC)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9466,29 +9576,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>$UH_MC</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>C25488</t>
+          <t>C49668</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.UH_NMC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dosing Frequency</t>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Inch</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Unit (UH_NMC)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9498,29 +9618,39 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>$UH_NMC</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>C89081</t>
+          <t>C48500</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.UW_MC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Investigational Therapy or Treatment</t>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kilogram</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Unit (UW_MC)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9530,29 +9660,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>$UW_MC</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>C41161</t>
+          <t>C28252</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.UW_NMC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Planned Country of Investigational Sites</t>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pound</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Unit (UW_NMC)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9562,29 +9702,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C71620</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>$UW_NMC</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>C98770</t>
+          <t>C48531</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VS.DOMAIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Planned Maximum Age of Subjects</t>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Domain Abbreviation (VS)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9594,29 +9744,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66734</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>$VSDOMAI</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>C49694</t>
+          <t>C49622</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSRESU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Planned Minimum Age of Subjects</t>
+          <t>Beats per Minute</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Beats per Minute</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Units for Vital Signs Orig Results</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9626,29 +9786,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>C49693</t>
+          <t>C49673</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSRESU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Planned Number of Subjects</t>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Centimeter</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Units for Vital Signs Orig Results</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9658,29 +9828,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>C49692</t>
+          <t>C49668</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSRESU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Route of Administration</t>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Kilogram</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Units for Vital Signs Orig Results</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9690,29 +9870,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>C38114</t>
+          <t>C28252</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSRESU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sex of Participants</t>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Millimeter of Mercury</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Units for Vital Signs Orig Results</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9722,29 +9912,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>C49696</t>
+          <t>C49670</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSRESU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Trial Blinding Schema</t>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Kilogram per Square Meter</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Units for Vital Signs Orig Results</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9754,29 +9954,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>$VSRESU</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>C49658</t>
+          <t>C49671</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Trial Indication Type</t>
+          <t>Body Mass Index</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9786,29 +9991,29 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>C49652</t>
+          <t>C16358</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Trial Length</t>
+          <t>Body Frame Size</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -9818,29 +10023,29 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>C49697</t>
+          <t>C49680</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Trial Phase Classification</t>
+          <t>Diastolic Blood Pressure</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -9850,29 +10055,29 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>C48281</t>
+          <t>C25299</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Trial Primary Objective</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9882,29 +10087,29 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>C85826</t>
+          <t>C25347</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trial Secondary Objective</t>
+          <t>Pulse Rate</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9914,29 +10119,29 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>C85827</t>
+          <t>C49676</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Trial Title</t>
+          <t>Systolic Blood Pressure</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9946,29 +10151,29 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>C49802</t>
+          <t>C25298</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTEST</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Trial Type</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Name</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -9978,29 +10183,34 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C67153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>C49660</t>
+          <t>C25208</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CL.TSPARM</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Trial is Randomized</t>
+          <t>BMI</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Body Mass Index</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Name</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10010,34 +10220,39 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C66741</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>C25196</t>
+          <t>C16358</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ADDON</t>
+          <t>DIABP</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Added on to Existing Treatments</t>
+          <t>Diastolic Blood Pressure</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -10047,39 +10262,39 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>C49703</t>
+          <t>C25299</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AGEMAX</t>
+          <t>FRMSIZE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Planned Maximum Age of Subjects</t>
+          <t>Body Frame Size</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -10089,39 +10304,39 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>C49694</t>
+          <t>C49680</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AGEMIN</t>
+          <t>HEIGHT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Planned Minimum Age of Subjects</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -10131,39 +10346,39 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>C49693</t>
+          <t>C25347</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AGESPAN</t>
+          <t>PULSE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Age Span</t>
+          <t>Pulse Rate</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10173,39 +10388,39 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>C20587</t>
+          <t>C49676</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AGEU</t>
+          <t>SYSBP</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Age Unit</t>
+          <t>Systolic Blood Pressure</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -10215,34 +10430,39 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>C25298</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CL.TSPARMCD</t>
+          <t>CL.VSTESTCD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>WEIGHT</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Dose per Administration</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trial Summary Parameter Test Code</t>
+          <t>Vital Signs Test Code</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10252,2220 +10472,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C66741</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>$TSPARMC</t>
+          <t>$VSTESTC</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>C25488</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>DOSFRQ</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Dosing Frequency</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>C89081</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>DOSU</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Dose Units</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>C73558</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>FCNTRY</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Planned Country of Investigational Sites</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>C98770</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>LENGTH</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Trial Length</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>C49697</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>OBJPRIM</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Trial Primary Objective</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>C85826</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>OBJSEC</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Trial Secondary Objective</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>C85827</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>PLANSUB</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Planned Number of Subjects</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>C49692</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>RANDOM</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Trial is Randomized</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>C25196</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Route of Administration</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>C38114</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>SEXPOP</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Sex of Participants</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>C49696</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SPONSOR</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Clinical Study Sponsor</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>C70793</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>TBLIND</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Trial Blinding Schema</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>C49658</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>TCNTRL</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Control Type</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>C49647</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>TINDTP</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Trial Indication Type</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>C49652</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Trial Title</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>C49802</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>TPHASE</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Trial Phase Classification</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>C48281</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>TRT</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Investigational Therapy or Treatment</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>C41161</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>CL.TSPARMCD</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>TTYPE</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Trial Type</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Trial Summary Parameter Test Code</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>C66738</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>$TSPARMC</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>C49660</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>CL.UH_MC</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Centimeter</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Unit (UH_MC)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>$UH_MC</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>C49668</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>CL.UH_NMC</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Inch</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Unit (UH_NMC)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>$UH_NMC</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>C48500</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>CL.UW_MC</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Kilogram</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Unit (UW_MC)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>$UW_MC</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>C28252</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>CL.UW_NMC</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Pound</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Unit (UW_NMC)</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>C71620</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>$UW_NMC</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>C48531</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>CL.VS.DOMAIN</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Vital Signs</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Domain Abbreviation (VS)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>C66734</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>$VSDOMAI</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>C49622</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>CL.VSRESU</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Beats per Minute</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Beats per Minute</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Units for Vital Signs Orig Results</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>C66770</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>$VSRESU</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>C49673</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>CL.VSRESU</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Centimeter</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Units for Vital Signs Orig Results</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>C66770</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>$VSRESU</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>C49668</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>CL.VSRESU</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Kilogram</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Units for Vital Signs Orig Results</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>C66770</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>$VSRESU</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>C28252</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>CL.VSRESU</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Millimeter of Mercury</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Units for Vital Signs Orig Results</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>C66770</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>$VSRESU</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>C49670</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>CL.VSRESU</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>kg/m2</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Kilogram per Square Meter</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Units for Vital Signs Orig Results</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>C66770</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>$VSRESU</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>C49671</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Body Mass Index</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>C16358</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Body Frame Size</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>C49680</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Diastolic Blood Pressure</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>C25299</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>C25347</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Pulse Rate</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>C49676</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Systolic Blood Pressure</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>C25298</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>CL.VSTEST</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Name</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>C67153</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
           <t>C25208</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>BMI</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Body Mass Index</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>C16358</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>DIABP</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Diastolic Blood Pressure</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>C25299</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>FRMSIZE</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Body Frame Size</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>C49680</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>HEIGHT</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>C25347</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>PULSE</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Pulse Rate</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>C49676</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>SYSBP</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Systolic Blood Pressure</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>C25298</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CL.VSTESTCD</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>WEIGHT</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Vital Signs Test Code</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>C66741</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>$VSTESTC</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>C25208</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CL.XSRESU</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>g/dL</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>g/dL</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Units for S Findings Results</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>$XSRESU</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>C64783</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>CL.XSRESU</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Units for S Findings Results</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>$XSRESU</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>C67015</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>CL.XSTEST</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>S Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>CL.XSTEST</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>S Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>CL.XSTEST</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>S Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>CL.XSTESTCD</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>TEST1</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>S Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>$XSTESTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>CL.XSTESTCD</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>TEST2</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>S Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>$XSTESTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>CL.XSTESTCD</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>TEST3</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>S Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>$XSTESTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>CL.XXRESU</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>g/dL</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>g/dL</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Units for X Findings Results</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>$XXRESU</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>C64783</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>CL.XXRESU</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Units for X Findings Results</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>$XXRESU</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>C67015</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>CL.XXRESU</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Units for X Findings Results</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>$XXRESU</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>C25613</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CL.XXTEST</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Test 11</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>X Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>CL.XXTEST</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Test 12</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>X Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>CL.XXTEST</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Test 13</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>X Findings Test Name</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CL.XXTESTCD</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>TEST11</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Test 11</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>X Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>$XXTESTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CL.XXTESTCD</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>TEST12</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Test 12</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>X Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>$XXTESTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CL.XXTESTCD</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>TEST13</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Test 13</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>X Findings Test Code</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>$XXTESTC</t>
         </is>
       </c>
     </row>
@@ -12476,7 +10493,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -12602,12 +10619,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT.CLSIG</t>
+          <t>MT.RACE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Algorithm to derive CLSIG</t>
+          <t>Algorithm to assign RACE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12617,19 +10634,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Only created if value qualifies as potentially clinically significant high or low based on the high and low ranges specified in the Statistical Analysis Plan.</t>
+          <t>Selected value converted to upper case to match CT.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT.ECENDY</t>
+          <t>MT.RDOMAIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Algorithm to derive ECENDY</t>
+          <t>Algorithm to derive RDOMAIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12639,20 +10656,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECENDY = ECENDTC-RFSTDTC+1 if ECENDTC is on or after RFSTDTC. 
-ECENDTC - RFSTDTC if ECENDTC precedes RFSTDTC.</t>
+          <t>Domain abbreviation from where data originated.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MT.EXDOSE</t>
+          <t>MT.RFENDTC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Algorithm to derive EXDOSE</t>
+          <t>Algorithm to derive RFENDTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12662,21 +10678,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>If ARMCD=WONDER10 then EXDOSE = Number of Tablets per Day (QVAL where QNAM=SMNO) * 10.
-If ARMCD=WONDER20 then EXDOSE = Number of Tablets per Day (QVAL where QNAM=SMNO) * 20.
-If ARMCD=PLACEBO then EXDOSE = 0.</t>
+          <t>RFENDTC = termination date, for safety subjects.
+Null for screen failures.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MT.EXDOSU</t>
+          <t>MT.RFSTDTC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Algorithm to derive EXDOSU</t>
+          <t>Algorithm to derive RFSTDTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12686,19 +10701,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Derived from ARM, ARMCD - equal to mg</t>
+          <t>RFSTDTC = first date/time of study drug, for safety subject.
+Null for screen failures.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MT.EXENDY</t>
+          <t>MT.SAFETY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Algorithm to derive EXENDY</t>
+          <t>Algorithm to derive the SAFETY population flag</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12708,20 +10724,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EXENDY = EXENDTC-RFSTDTC+1 if EXENDTC is on or after RFSTDTC.
-EXENDTC - RFSTDTC if EXENDTC precedes RFSTDTC.</t>
+          <t>SAFETY = "Y" for randomized subjects who took at least one dose study medication. Null otherwise.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT.EXSTDY</t>
+          <t>MT.SEQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Algorithm to derive EXSTDY</t>
+          <t>Algorithm to derive SEQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12731,20 +10746,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EXSTDY = EXSTDTC - RFSTDTC+1 if EXSTDTC is on or after RFSTDTC.
-EXSTDTC - RFSTDTC if EXSTDTC precedes RFSTDTC.</t>
+          <t>Sequential number identifying records within each USUBJID in the domain.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT.EXTRT</t>
+          <t>MT.TSSEQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Algorithm to derive EXTRT</t>
+          <t>Algorithm to derive TSSEQ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12754,19 +10768,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Derived from ARM, ARMCD</t>
+          <t>Sequential number identifying records within each TSPARM in the domain.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT.LBBLFL</t>
+          <t>MT.USUBJID</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Algorithm to derive LBBLFL</t>
+          <t>Algorithm to derive USUBJID</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12776,20 +10790,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Safety subjects only: LBBLFL = "Y" for last record with non Null LBORRES on or before the first dose date (RFSTDTC).
-Null otherwise.</t>
+          <t>Concatenation of STUDYID and SUBJID</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT.LBDY</t>
+          <t>MT.VSBLFL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Algorithm to derive LBDY</t>
+          <t>Algorithm to derive VSBLFL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12799,19 +10812,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LBDY = LBDTC-RFSTDTC+1 if LBDTC is on or after RFSTDTC. LBDTC - RFSTDTC if LBDTC precedes RFSTDTC.</t>
+          <t>Safety subjects only: VSBLFL = "Y" for last record with non Null VSORRES on or before the first dose date (RFSTDTC).
+Null otherwise.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MT.LBNRIND</t>
+          <t>MT.VSDY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Algorithm to derive LBNRIND</t>
+          <t>Algorithm to derive VSDY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12821,19 +10835,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Reference Range Indicator based upon standard results and ranges.</t>
+          <t>VSDY = VSDTC-RFSTDTC+1 if VSDTC is on or after RFSTDTC. VSDTC - RFSTDTC if VSDTC precedes RFSTDTC.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MT.RACE</t>
+          <t>MT.VSSTRESC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Algorithm to assign RACE</t>
+          <t>Algorithm to derive VSSTRESC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12843,19 +10857,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Selected value converted to upper case to match CT.</t>
+          <t>Data collected in non-standard units (i.e. lbs, inches) is converted using standard conversion factors to standard units (kg, cm).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MT.RDOMAIN</t>
+          <t>MT.VSSTRESN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Algorithm to derive RDOMAIN</t>
+          <t>Algorithm to derive VSSTRESN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12865,414 +10879,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Domain abbreviation from where data originated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MT.RFENDTC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Algorithm to derive RFENDTC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>RFENDTC = termination date, for safety subjects.
-Null for screen failures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MT.RFSTDTC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Algorithm to derive RFSTDTC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>RFSTDTC = first date/time of study drug, for safety subject.
-Null for screen failures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MT.SAFETY</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Algorithm to derive the SAFETY population flag</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SAFETY = "Y" for randomized subjects who took at least one dose study medication. Null otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MT.SEQ</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Algorithm to derive SEQ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sequential number identifying records within each USUBJID in the domain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MT.TSSEQ</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Algorithm to derive TSSEQ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sequential number identifying records within each TSPARM in the domain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MT.USUBJID</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Algorithm to derive USUBJID</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Concatenation of STUDYID and SUBJID</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MT.VSBLFL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Algorithm to derive VSBLFL</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Safety subjects only: VSBLFL = "Y" for last record with non Null VSORRES on or before the first dose date (RFSTDTC).
-Null otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MT.VSDY</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Algorithm to derive VSDY</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VSDY = VSDTC-RFSTDTC+1 if VSDTC is on or after RFSTDTC. VSDTC - RFSTDTC if VSDTC precedes RFSTDTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MT.VSSTRESC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Algorithm to derive VSSTRESC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Data collected in non-standard units (i.e. lbs, inches) is converted using standard conversion factors to standard units (kg, cm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MT.VSSTRESN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Algorithm to derive VSSTRESN</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
           <t>VSSTRESN = numeric value of VSSTRESC, when VSSTRESC contains numeric data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MT.XSBLFL</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XSBLFL</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Safety subjects only: XSBLFL = "Y" for last record with non Null XSORRES on or before the first dose date (RFSTDTC).
-Null otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MT.XSDY</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XSDY</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>XSDY = XSDTC-RFSTDTC+1 if XSDTC is on or after RFSTDTC. XSDTC - RFSTDTC if XSDTC precedes RFSTDTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MT.XSSTRESC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XSSTRESC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Data collected in non-standard units (i.e. lbs, inches) is converted using standard conversion factors to standard units (kg, cm).
-BMI is calculated by the EDC system (operationally derived) as follows:
- round((XSSTRESN for weight/ (XSSTRESN for height / 100)^2), .01).
- Note: If height is not collected at a visit, use the height collected at screening.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MT.XSSTRESN</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XSSTRESN</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>XSSTRESN = numeric value of XSSTRESC, when XSSTRESC contains numeric data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MT.XXBLFL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XXBLFL</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Safety subjects only: XXBLFL = "Y" for last record with non Null XXORRES on or before the first dose date (RFSTDTC).
-Null otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MT.XXDY</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XXDY</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>XXDY = XXDTC-RFSTDTC+1 if XXDTC is on or after RFSTDTC. XXDTC - RFSTDTC if XXDTC precedes RFSTDTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MT.XXSTRESC</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XXSTRESC</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Data collected in non-standard units (i.e. lbs, inches) is converted using standard conversion factors to standard units (kg, cm).
-BMI is calculated by the EDC system (operationally derived) as follows:
- round((XXSTRESN for weight/ (XXSTRESN for height / 100)^2), .01).
- Note: If height is not collected at a visit, use the height collected at screening.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MT.XXSTRESN</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Algorithm to derive XXSTRESN</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Computation</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>XXSTRESN = numeric value of XXSTRESC, when XXSTRESC contains numeric data.</t>
         </is>
       </c>
     </row>
@@ -13283,7 +10890,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -13388,298 +10995,190 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COM.CT2-EC</t>
+          <t>COM.CT2-SEX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Domain codelist was updated when SDTMIG 3.2 became production. Referencing a newer CT version that includes the revised codelist</t>
+          <t>The term "UN" was changed to "UNDIFERENTIATED" for codelist "SEX" on the 2014-03-28 CT release. Referencing the codelist from a newer release since the new release includes other codelists used in the study.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COM.CT2-SEX</t>
+          <t>COM.DOMAIN.DM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The term "UN" was changed to "UNDIFERENTIATED" for codelist "SEX" on the 2014-03-28 CT release. Referencing the codelist from a newer release since the new release includes other codelists used in the study.</t>
+          <t>See Reviewer's Guide, Section 2.1 Demographics</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LF.csdrg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>section2.1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COM.DOMAIN.DI</t>
+          <t>COM.IDVAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The DI domain is included to illustrate the use of a separate complementary SDTMIG. In this example, the device ID is referenced from a Findings Domain (XS).</t>
+          <t>Name of the variables for the related records.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COM.DOMAIN.DM</t>
+          <t>COM.IDVARVAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>See Reviewer's Guide, Section 2.1 Demographics</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LF.csdrg</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>section2.1</t>
+          <t>Value of identifying variable described in IDVAR.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COM.IDVAR</t>
+          <t>COM.RACE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name of the variables for the related records.</t>
+          <t>Note that the study protocol has been amended to not allow the specification of other race per current regulatory requirements. Refer to FDA Guidance XYZ and PMDA Guidance P-XYZ.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COM.IDVARVAL</t>
+          <t>COM.STD1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Value of identifying variable described in IDVAR.</t>
+          <t>The CDISC01 study was modeled on a very old SDTMIG and no attempt was done yet to upversion it to a newer SDTMIG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COM.ISO3166</t>
+          <t>COM.STD2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The code values used are the Alpha-3 codes</t>
+          <t>As an example, the CDISC01 study was adjusted to include a new Domain available in SDTM IG 3.2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COM.LBNRIND</t>
+          <t>COM.STD3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Assuming the LBNRIND is derived by the vendor</t>
+          <t>As an example, the CDISC01 study was adjusted to include a new Domain available in SDTMIG-MD 1.0. The XS Domain is expected to reference the device used with variable SPDEVID.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COM.LBORRES</t>
+          <t>COM.STD5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Origin specified at Value Level Metadata</t>
+          <t>This is the CDISC CT Package 60 (2025-09-29) associated to the CDISC Define-XML Specification Version 2.1.10.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COM.LBORRESU(Repeated)</t>
+          <t>COM.STUDY.DATA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Note this example does not include VLM for this variable since it is just an example and the way to specify VLM is illustrated for LBORRESU.</t>
+          <t>The data submitted only includes subjects in the USA since other sites did not enroll any subjects.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COM.LBREFID</t>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accession number</t>
+          <t>Join any Subject Level dataset with the Demographics dataset based on [IG.datasetname]IT.USUBJID = [IG.DM]IT.USUBJID, assuming 'IG.datasetname' is the OID of the ItemGroupDef that defines the subject-level dataset to be joined with the Demographics dataset.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COM.RACE</t>
+          <t>COM.VS.VISITNUM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Note that the study protocol has been amended to not allow the specification of other race per current regulatory requirements. Refer to FDA Guidance XYZ and PMDA Guidance P-XYZ.</t>
+          <t>Assigned from the TV domain based on the VISIT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COM.RESU</t>
+          <t>COM.VSSTRESC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Planned Numeric tests were not performed.</t>
+          <t>Testing a comment in addition to a method: BMI is derived and the specific method is provided at VLM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COM.STD1</t>
+          <t>COM.VSSTRESN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The CDISC01 study was modeled on a very old SDTMIG and no attempt was done yet to upversion it to a newer SDTMIG</t>
+          <t>Testing a comment in addition to a method: BMI is operationally derived and the specific method is provided at VLM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COM.STD2</t>
+          <t>COM.VSSTRESU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>As an example, the CDISC01 study was adjusted to include a new Domain available in SDTM IG 3.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>COM.STD3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>As an example, the CDISC01 study was adjusted to include a new Domain available in SDTMIG-MD 1.0. The XS Domain is expected to reference the device used with variable SPDEVID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>This is the CDISC CT Package 60 (2025-09-29) associated to the CDISC Define-XML Specification Version 2.1.10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>COM.STUDY.DATA</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>The data submitted only includes subjects in the USA since other sites did not enroll any subjects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Join any Subject Level dataset with the Demographics dataset based on [IG.datasetname]IT.USUBJID = [IG.DM]IT.USUBJID, assuming 'IG.datasetname' is the OID of the ItemGroupDef that defines the subject-level dataset to be joined with the Demographics dataset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>COM.VS.VISITNUM</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Assigned from the TV domain based on the VISIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>COM.VSSTRESC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Testing a comment in addition to a method: BMI is derived and the specific method is provided at VLM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>COM.VSSTRESN</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Testing a comment in addition to a method: BMI is operationally derived and the specific method is provided at VLM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>COM.VSSTRESU</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
           <t>Standard units consistent with CDISC controlled terminology</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>COM.XX</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Special domain contingent on rare conditions observed.</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -15,8 +15,7 @@
     <sheet name="Methods" sheetId="6" r:id="rId6"/>
     <sheet name="Comments" sheetId="7" r:id="rId7"/>
     <sheet name="Documents" sheetId="8" r:id="rId8"/>
-    <sheet name="WhereClauses" sheetId="9" r:id="rId9"/>
-    <sheet name="Standards" sheetId="10" r:id="rId10"/>
+    <sheet name="Standards" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,260 +535,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Publishing Set</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STD.1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SDTMIG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IG</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.1.2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>COM.STD1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STD.2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SDTMIG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IG</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>COM.STD2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STD.2_1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SDTMIG-MD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COM.STD3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STD.3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2011-12-09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COM.CT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STD.4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2015-12-18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COM.CT2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STD.5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CDISC/NCI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DEFINE-XML</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N5"/>
@@ -3965,7 +3710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4041,72 +3786,27 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>where_clause_id</t>
+          <t>Assigned Value</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>itemoid</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sas_field_name</t>
+          <t>Pages</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Predecessor</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>origin_description</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>origin_document_id</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>pages</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>page_type</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>page_title</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>role_codelist_id</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>value_list_id</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>predecessor</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>assigned_value</t>
+          <t>Origin Document</t>
         </is>
       </c>
     </row>
@@ -4126,7 +3826,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE1</t>
+          <t>QNAM EQ RACE1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4162,44 +3862,19 @@
           <t>MT.RACE</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.RACE1</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.RACE1</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>RACE1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4219,7 +3894,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE2</t>
+          <t>QNAM EQ RACE2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4255,44 +3930,19 @@
           <t>MT.RACE</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.RACE2</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.RACE2</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>RACE2</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4312,7 +3962,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE3</t>
+          <t>QNAM EQ RACE3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4348,44 +3998,19 @@
           <t>MT.RACE</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.RACE3</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.RACE3</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>RACE3</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4030,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RAND</t>
+          <t>QNAM EQ RAND</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4436,44 +4061,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.RAND</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.RAND</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>RAND</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4093,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RANDNO</t>
+          <t>QNAM EQ RANDNO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4519,44 +4119,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.RANDNO</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.RANDNO</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RANDNO</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4151,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.SAFETY</t>
+          <t>QNAM EQ SAFETY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4612,29 +4187,9 @@
           <t>MT.SAFETY</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>WC.SUPPDM.QNAM.SAFETY</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>IT.SUPPDM.QVAL.SAFETY</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>SAFETY</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
           <t>Sponsor</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Record Qualifier</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4209,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.AGEMAX</t>
+          <t>TSPARMCD EQ AGEMAX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4680,22 +4235,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEMAX</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.AGEMAX</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>AGEMAX</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -4717,7 +4257,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.AGEMIN</t>
+          <t>TSPARMCD EQ AGEMIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4743,22 +4283,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEMIN</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.AGEMIN</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>AGEMIN</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -4780,7 +4305,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.AGEU</t>
+          <t>TSPARMCD EQ AGEU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4811,22 +4336,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEU</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.AGEU</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>AGEU</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -4848,7 +4358,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.DOSE</t>
+          <t>TSPARMCD EQ DOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4874,22 +4384,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.DOSE</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.DOSE</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>DOSE</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -4911,7 +4406,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.FCNTRY</t>
+          <t>TSPARMCD EQ FCNTRY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4942,22 +4437,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.FCNTRY</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.FCNTRY</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>FCNTRY</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -4979,7 +4459,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WC.TS.TSPARMCD.PLANSUB</t>
+          <t>TSPARMCD EQ PLANSUB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5005,22 +4485,7 @@
           <t>Protocol</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.PLANSUB</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>IT.TS.TSVAL.PLANSUB</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>PLANSUB</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
@@ -5042,7 +4507,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
+          <t>VSTESTCD EQ DIABP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5068,39 +4533,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.DIABP</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>DIABPOR</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5120,7 +4565,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+          <t>VSTESTCD EQ FRMSIZE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5151,39 +4596,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.FRMSIZE</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.FRMSIZE</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>FRMSZOR</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5203,7 +4628,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
+          <t>VSTESTCD EQ HEIGHT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5237,39 +4662,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.HEIGHT</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>HEIGHTOR</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5289,7 +4694,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
+          <t>VSTESTCD EQ PULSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5315,39 +4720,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.PULSE</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>PULSEOR</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5367,7 +4752,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
+          <t>VSTESTCD EQ SYSBP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5393,39 +4778,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.SYSBP</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>SYSBPOR</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5445,7 +4810,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
+          <t>VSTESTCD EQ WEIGHT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5479,39 +4844,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRES.WEIGHT</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>WEIGHTOR</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -5531,7 +4876,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
+          <t>VSTESTCD EQ DIABP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5550,21 +4895,6 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.DIABP</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>DIABPSC</t>
         </is>
       </c>
     </row>
@@ -5584,7 +4914,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+          <t>VSTESTCD EQ FRMSIZE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5608,21 +4938,6 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>CL.SIZE</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.FRMSIZE</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.FRMSIZE</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>FRMSZSC</t>
         </is>
       </c>
     </row>
@@ -5642,7 +4957,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
+          <t>VSTESTCD EQ HEIGHT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5669,21 +4984,6 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.HEIGHT</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>HEIGHTSC</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5003,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
+          <t>VSTESTCD EQ PULSE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5722,21 +5022,6 @@
       <c r="J23" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.PULSE</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>PULSESC</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5041,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
+          <t>VSTESTCD EQ SYSBP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5775,21 +5060,6 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.SYSBP</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>SYSBPSC</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5079,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
+          <t>VSTESTCD EQ WEIGHT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5836,21 +5106,6 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.WEIGHT</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>WEIGHTSC</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5125,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.BMI</t>
+          <t>VSTESTCD EQ BMI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5902,21 +5157,6 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>MT.BMISC</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.BMI</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESC.BMI</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>BMISC</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5176,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
+          <t>VSTESTCD EQ DIABP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5955,21 +5195,6 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESN.DIABP</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>DIABPSN</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5214,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
+          <t>VSTESTCD EQ HEIGHT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6016,21 +5241,6 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESN.HEIGHT</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>HEIGHTSN</t>
         </is>
       </c>
     </row>
@@ -6050,7 +5260,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
+          <t>VSTESTCD EQ PULSE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6069,21 +5279,6 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESN.PULSE</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>PULSESN</t>
         </is>
       </c>
     </row>
@@ -6103,7 +5298,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
+          <t>VSTESTCD EQ SYSBP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6122,21 +5317,6 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESN.SYSBP</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>SYSBPSN</t>
         </is>
       </c>
     </row>
@@ -6156,7 +5336,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
+          <t>VSTESTCD EQ WEIGHT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6183,21 +5363,6 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>IT.VS.VSSTRESN.WEIGHT</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>WEIGHTSN</t>
         </is>
       </c>
     </row>
@@ -6217,7 +5382,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.BMI</t>
+          <t>VSTESTCD EQ BMI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6256,44 +5421,19 @@
           <t>MT.BMISN</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.BMI</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>IT.VS.VSSTRESN.BMI</t>
+          <t>Sponsor</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>BMISN</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Sponsor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>EDC System</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -6313,7 +5453,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+          <t>VSTESTCD EQ HEIGHT and DM.COUNTRY IN (CAN, MEX)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6349,39 +5489,19 @@
           <t>COM.STUDY.DATA</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRESU.HEIGHT.DM.COUNTRY.CMETRIC</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>HEIGHTOM</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -6401,7 +5521,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+          <t>VSTESTCD EQ HEIGHT and DM.COUNTRY EQ USA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6432,39 +5552,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRESU.HEIGHT.DM.COUNTRY.CNMETRIC</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>HEIGHTON</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -6484,7 +5584,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+          <t>VSTESTCD EQ WEIGHT and DM.COUNTRY IN (CAN, MEX)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6520,39 +5620,19 @@
           <t>COM.STUDY.DATA</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRESU.WEIGHT.DM.COUNTRY.CMETRIC</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>WEIGHTOM</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -6572,7 +5652,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+          <t>VSTESTCD EQ WEIGHT and DM.COUNTRY EQ USA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6603,39 +5683,19 @@
           <t>Collected</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>IT.VS.VSORRESU.WEIGHT.DM.COUNTRY.CNMETRIC</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>WEIGHTON</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Investigator</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>LF.acrf</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>PhysicalRef</t>
         </is>
       </c>
     </row>
@@ -6646,7 +5706,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6692,10 +5752,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>NCI Term Code</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
@@ -6730,7 +5795,7 @@
           <t>C66781</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>C29848</t>
         </is>
@@ -6995,6 +6060,11 @@
           <t>$COUNTRY</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COM.COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7027,6 +6097,11 @@
           <t>$COUNTRY</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COM.COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7059,6 +6134,11 @@
           <t>$COUNTRY</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COM.COUNTRY</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7096,7 +6176,7 @@
           <t>$DMDOMAI</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>C49572</t>
         </is>
@@ -7128,7 +6208,7 @@
           <t>C66790</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>C17459</t>
         </is>
@@ -7160,7 +6240,7 @@
           <t>C66790</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>C41222</t>
         </is>
@@ -7202,7 +6282,7 @@
           <t>$NY</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>C49488</t>
         </is>
@@ -7244,7 +6324,7 @@
           <t>$NY</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>C49487</t>
         </is>
@@ -7286,7 +6366,7 @@
           <t>$NY</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>C17998</t>
         </is>
@@ -7321,7 +6401,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>C41261</t>
         </is>
@@ -7356,7 +6436,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>C41259</t>
         </is>
@@ -7391,7 +6471,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>C16352</t>
         </is>
@@ -7426,7 +6506,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>C41260</t>
         </is>
@@ -7461,7 +6541,7 @@
           <t>C74457</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>C41219</t>
         </is>
@@ -7505,6 +6585,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>COM.CT2-SEX</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>C16576</t>
         </is>
       </c>
@@ -7547,6 +6632,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>COM.CT2-SEX</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>C20197</t>
         </is>
       </c>
@@ -7589,6 +6679,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>COM.CT2-SEX</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>C17998</t>
         </is>
       </c>
@@ -7631,6 +6726,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>COM.CT2-SEX</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>C17998</t>
         </is>
       </c>
@@ -7661,12 +6761,12 @@
           <t>C66733</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>C25376</t>
         </is>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>1</v>
       </c>
     </row>
@@ -7696,12 +6796,12 @@
           <t>C66733</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>C49507</t>
         </is>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>2</v>
       </c>
     </row>
@@ -7731,12 +6831,12 @@
           <t>C66733</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>C49508</t>
         </is>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>3</v>
       </c>
     </row>
@@ -7776,7 +6876,7 @@
           <t>$TSDOMAI</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>C53483</t>
         </is>
@@ -7808,7 +6908,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>C49703</t>
         </is>
@@ -7840,7 +6940,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>C20587</t>
         </is>
@@ -7899,7 +6999,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>C70793</t>
         </is>
@@ -7931,7 +7031,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>C49647</t>
         </is>
@@ -7963,7 +7063,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>C73558</t>
         </is>
@@ -7995,7 +7095,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>C25488</t>
         </is>
@@ -8027,7 +7127,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>C89081</t>
         </is>
@@ -8059,7 +7159,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>C41161</t>
         </is>
@@ -8091,7 +7191,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>C98770</t>
         </is>
@@ -8123,7 +7223,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>C49694</t>
         </is>
@@ -8155,7 +7255,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>C49693</t>
         </is>
@@ -8187,7 +7287,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>C49692</t>
         </is>
@@ -8219,7 +7319,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>C38114</t>
         </is>
@@ -8251,7 +7351,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>C49696</t>
         </is>
@@ -8283,7 +7383,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>C49658</t>
         </is>
@@ -8315,7 +7415,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>C49652</t>
         </is>
@@ -8347,7 +7447,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>C49697</t>
         </is>
@@ -8379,7 +7479,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>C48281</t>
         </is>
@@ -8411,7 +7511,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>C85826</t>
         </is>
@@ -8443,7 +7543,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>C85827</t>
         </is>
@@ -8475,7 +7575,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>C49802</t>
         </is>
@@ -8507,7 +7607,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>C49660</t>
         </is>
@@ -8539,7 +7639,7 @@
           <t>C67152</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>C25196</t>
         </is>
@@ -8581,7 +7681,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>C49703</t>
         </is>
@@ -8623,7 +7723,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>C49694</t>
         </is>
@@ -8665,7 +7765,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>C49693</t>
         </is>
@@ -8707,7 +7807,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>C20587</t>
         </is>
@@ -8786,7 +7886,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>C25488</t>
         </is>
@@ -8828,7 +7928,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>C89081</t>
         </is>
@@ -8870,7 +7970,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>C73558</t>
         </is>
@@ -8912,7 +8012,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>C98770</t>
         </is>
@@ -8954,7 +8054,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>C49697</t>
         </is>
@@ -8996,7 +8096,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>C85826</t>
         </is>
@@ -9038,7 +8138,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>C85827</t>
         </is>
@@ -9080,7 +8180,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>C49692</t>
         </is>
@@ -9122,7 +8222,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>C25196</t>
         </is>
@@ -9164,7 +8264,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>C38114</t>
         </is>
@@ -9206,7 +8306,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>C49696</t>
         </is>
@@ -9248,7 +8348,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>C70793</t>
         </is>
@@ -9290,7 +8390,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>C49658</t>
         </is>
@@ -9332,7 +8432,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>C49647</t>
         </is>
@@ -9374,7 +8474,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>C49652</t>
         </is>
@@ -9416,7 +8516,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>C49802</t>
         </is>
@@ -9458,7 +8558,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>C48281</t>
         </is>
@@ -9500,7 +8600,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>C41161</t>
         </is>
@@ -9542,7 +8642,7 @@
           <t>$TSPARMC</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>C49660</t>
         </is>
@@ -9584,7 +8684,7 @@
           <t>$UH_MC</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>C49668</t>
         </is>
@@ -9626,7 +8726,7 @@
           <t>$UH_NMC</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>C48500</t>
         </is>
@@ -9668,7 +8768,7 @@
           <t>$UW_MC</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>C28252</t>
         </is>
@@ -9710,7 +8810,7 @@
           <t>$UW_NMC</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>C48531</t>
         </is>
@@ -9752,7 +8852,7 @@
           <t>$VSDOMAI</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>C49622</t>
         </is>
@@ -9794,7 +8894,7 @@
           <t>$VSRESU</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>C49673</t>
         </is>
@@ -9836,7 +8936,7 @@
           <t>$VSRESU</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>C49668</t>
         </is>
@@ -9878,7 +8978,7 @@
           <t>$VSRESU</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>C28252</t>
         </is>
@@ -9920,7 +9020,7 @@
           <t>$VSRESU</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>C49670</t>
         </is>
@@ -9962,7 +9062,7 @@
           <t>$VSRESU</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>C49671</t>
         </is>
@@ -9994,7 +9094,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>C16358</t>
         </is>
@@ -10026,7 +9126,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>C49680</t>
         </is>
@@ -10058,7 +9158,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>C25299</t>
         </is>
@@ -10090,7 +9190,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>C25347</t>
         </is>
@@ -10122,7 +9222,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>C49676</t>
         </is>
@@ -10154,7 +9254,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>C25298</t>
         </is>
@@ -10186,7 +9286,7 @@
           <t>C67153</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>C25208</t>
         </is>
@@ -10228,7 +9328,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>C16358</t>
         </is>
@@ -10270,7 +9370,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>C25299</t>
         </is>
@@ -10312,7 +9412,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>C49680</t>
         </is>
@@ -10354,7 +9454,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>C25347</t>
         </is>
@@ -10396,7 +9496,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>C49676</t>
         </is>
@@ -10438,7 +9538,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>C25298</t>
         </is>
@@ -10480,7 +9580,7 @@
           <t>$VSTESTC</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>C25208</t>
         </is>
@@ -11485,7 +10585,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11496,25 +10596,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Comparator</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -11523,769 +10628,207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE1</t>
+          <t>STD.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>SDTMIG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RACE1</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COM.STD1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE2</t>
+          <t>STD.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>SDTMIG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RACE2</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STD2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RACE3</t>
+          <t>STD.2_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>SDTMIG-MD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RACE3</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STD3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RAND</t>
+          <t>STD.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>CDISC/NCI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>2011-12-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAND</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.CT1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.RANDNO</t>
+          <t>STD.4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>CDISC/NCI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>2015-12-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RANDNO</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COM.CT2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WC.SUPPDM.QNAM.SAFETY</t>
+          <t>STD.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SUPPDM</t>
+          <t>CDISC/NCI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QNAM</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EQ</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SAFETY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEMAX</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AGEMAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEMIN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AGEMIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.AGEU</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AGEU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.DOSE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>DOSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.FCNTRY</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>FCNTRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WC.TS.TSPARMCD.PLANSUB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TSPARMCD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PLANSUB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.BMI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BMI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.DIABP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>DIABP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.FRMSIZE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>FRMSIZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HEIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HEIGHT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>COUNTRY</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(CAN, MEX)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>HEIGHT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>COUNTRY</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.PULSE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PULSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.SYSBP</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SYSBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>WEIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>WEIGHT</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>COUNTRY</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(CAN, MEX)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>VSTESTCD</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>WEIGHT</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>COUNTRY</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>COM.SUBJECTDATA-JOIN-DM</t>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -359,7 +359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,156 +377,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>define_version</t>
+          <t>StudyName</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.1.10</t>
+          <t>CDISC01_1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>study_oid</t>
+          <t>StudyDescription</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STDY.www.cdisc.org.CDISC01_1</t>
+          <t>CDISC Test Study Modified to illustrate Define-XML 2.1 features</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>file_oid</t>
+          <t>ProtocolName</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>www.cdisc.org/StudyCDISC01_1/1/Define-XML_2.1.0</t>
+          <t>CDISC01-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>odm_context</t>
+          <t>DefineVersion</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>2.1.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>metadata_version_oid</t>
+          <t>StudyOID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MDV.CDISC01_1.1.SDTMIG.3.1.2.SDTM.1.2_X</t>
+          <t>STDY.www.cdisc.org.CDISC01_1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>metadata_version_name</t>
+          <t>FileOID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Study CDISC01_1, Data Definitions V-1</t>
+          <t>www.cdisc.org/StudyCDISC01_1/1/Define-XML_2.1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>metadata_version_description</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Data Definitions for CDISC01-01 SDTM datasets. This metadata version contains only a subset of datasets compared to the prior version. The metadata provided is only intended to illustrate most Define-XML 2.1 new features and not meant to serve as a comprehensive example of all metadata expected to be defined to fully describe an SDTM dataset package.   Notes:   1) Supplemental documents released in prior Define-XML versions were not updated to reflect changes to the metadata.    2) This example is prepared for a context other than submission; however, still using the approach of non-standard variables prepared as supplemental qualifiers datasets.</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>originator</t>
+          <t>MetaDataVersionOID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CDISC Data Exchange Standards Team</t>
+          <t>MDV.CDISC01_1.1.SDTMIG.3.1.2.SDTM.1.2_X</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>source_system</t>
+          <t>MetaDataVersionName</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.Hungria-System</t>
+          <t>Study CDISC01_1, Data Definitions V-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source_system_version</t>
+          <t>MetaDataVersionDescription</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.1-A1</t>
+          <t>Data Definitions for CDISC01-01 SDTM datasets. This metadata version contains only a subset of datasets compared to the prior version. The metadata provided is only intended to illustrate most Define-XML 2.1 new features and not meant to serve as a comprehensive example of all metadata expected to be defined to fully describe an SDTM dataset package.   Notes:   1) Supplemental documents released in prior Define-XML versions were not updated to reflect changes to the metadata.    2) This example is prepared for a context other than submission; however, still using the approach of non-standard variables prepared as supplemental qualifiers datasets.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>StudyName</t>
+          <t>Originator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDISC01_1</t>
+          <t>CDISC Data Exchange Standards Team</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>StudyDescription</t>
+          <t>SourceSystem</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CDISC Test Study Modified to illustrate Define-XML 2.1 features</t>
+          <t>M.Hungria-System</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ProtocolName</t>
+          <t>SourceSystemVersion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CDISC01-1</t>
+          <t>2.1-A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>StandardName</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SDTM-IG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>StandardVersion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
         </is>
       </c>
     </row>
@@ -9692,6 +9716,16 @@
           <t>character value of VSSTRESN</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SAS 9.0 or later as a macro call. Macro developed as a standard macro that returns a value to be assigned as part of a data step assignment or proc sql select and update statements. Notes: 1) need to be able to specify more information about the context of a method, the method version and corresponding input parameters. For ODMv1.3.2 / Define-XML 2.1 free-text. 2) As an example, included a version of the code handled on the macro name as it can be defined by the user somehwere in the metadata definition for the method to be used. </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>%convert_to_character_versionx(numeric_value=bmi_numeric_value,length=bmi_defined_lenght,sd=bmi_defined_sd)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9713,6 +9747,16 @@
         <is>
           <t>round((VSSTRESN for weight/ (VSSTRESN for height / 100)^2), .01).
 Note: height and weight at the closest visit collected.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SAS 9.0 or later as a macro call. Macro developed as a standard macro that returns a value to be assigned as part of a data step assignment or proc sql select and update statements. Notes: 1) need to be able to specify more information about the context of a method, the method version and corresponding input parameters. For ODMv1.3.2 / Define-XML 2.1 free-text. 2) As an example, included a version of the code handled on the macro name as it can be defined by the user somehwere in the metadata definition for the method to be used. </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>%bmisn_versionx(weight=retrieved_weight_closest_visit,height=retrieved_height_closest_visit)</t>
         </is>
       </c>
     </row>

--- a/inst/extdata/sdtm-spec.xlsx
+++ b/inst/extdata/sdtm-spec.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Define" sheetId="1" r:id="rId1"/>
+    <sheet name="Study" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="Variables" sheetId="3" r:id="rId3"/>
     <sheet name="ValueLevel" sheetId="4" r:id="rId4"/>
@@ -15,7 +15,9 @@
     <sheet name="Methods" sheetId="6" r:id="rId6"/>
     <sheet name="Comments" sheetId="7" r:id="rId7"/>
     <sheet name="Documents" sheetId="8" r:id="rId8"/>
-    <sheet name="Standards" sheetId="9" r:id="rId9"/>
+    <sheet name="WhereClauses" sheetId="9" r:id="rId9"/>
+    <sheet name="Dictionaries" sheetId="10" r:id="rId10"/>
+    <sheet name="Standards" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,6 +561,339 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dictionary</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Href</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CL.ISO.COUNTRY</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Country Codes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ISO-3166 (Country Codes)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2013-11-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/iso-3166-country-codes.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Publishing Set</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STD.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SDTMIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COM.STD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STD.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SDTMIG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COM.STD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STD.2_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SDTMIG-MD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COM.STD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STD.3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2011-12-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COM.CT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STD.4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2015-12-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SDTM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COM.CT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STD.5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDISC/NCI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DEFINE-XML</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COM.STD5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N5"/>
@@ -2172,6 +2507,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>CL.ISO.COUNTRY</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>Assigned</t>
@@ -3734,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3833,6 +4173,11 @@
           <t>Origin Document</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -3850,7 +4195,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QNAM EQ RACE1</t>
+          <t>WC.SUPPDM.QNAM.RACE1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3899,6 +4244,11 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Race 1</t>
         </is>
       </c>
     </row>
@@ -3918,7 +4268,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QNAM EQ RACE2</t>
+          <t>WC.SUPPDM.QNAM.RACE2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3967,6 +4317,11 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Race 2</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4341,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>QNAM EQ RACE3</t>
+          <t>WC.SUPPDM.QNAM.RACE3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4035,6 +4390,11 @@
       <c r="S4" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Race 3</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4414,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QNAM EQ RAND</t>
+          <t>WC.SUPPDM.QNAM.RAND</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4098,6 +4458,11 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Randomized Population Flag</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4482,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QNAM EQ RANDNO</t>
+          <t>WC.SUPPDM.QNAM.RANDNO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4156,6 +4521,11 @@
       <c r="S6" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Randomization Number</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4545,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>QNAM EQ SAFETY</t>
+          <t>WC.SUPPDM.QNAM.SAFETY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4214,6 +4584,11 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Safety Population Flag</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4608,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ AGEMAX</t>
+          <t>WC.TS.TSPARMCD.AGEMAX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4262,6 +4637,11 @@
       <c r="P8" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4661,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ AGEMIN</t>
+          <t>WC.TS.TSPARMCD.AGEMIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4310,6 +4690,11 @@
       <c r="P9" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4714,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ AGEU</t>
+          <t>WC.TS.TSPARMCD.AGEU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4363,6 +4748,11 @@
       <c r="P10" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Age Unit</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4772,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ DOSE</t>
+          <t>WC.TS.TSPARMCD.DOSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4411,6 +4801,11 @@
       <c r="P11" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dose per Administration</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4825,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ FCNTRY</t>
+          <t>WC.TS.TSPARMCD.FCNTRY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4464,6 +4859,11 @@
       <c r="P12" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4883,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TSPARMCD EQ PLANSUB</t>
+          <t>WC.TS.TSPARMCD.PLANSUB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4512,6 +4912,11 @@
       <c r="P13" t="inlineStr">
         <is>
           <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Planned Number of Subjects</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4936,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ DIABP</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4570,6 +4975,11 @@
       <c r="S14" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Diastolic Blood Pressure in Orig U</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4999,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ FRMSIZE</t>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4633,6 +5043,11 @@
       <c r="S15" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Body Frame Size - Orig</t>
         </is>
       </c>
     </row>
@@ -4652,7 +5067,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ HEIGHT</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4699,6 +5114,11 @@
       <c r="S16" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Height in Orig U</t>
         </is>
       </c>
     </row>
@@ -4718,7 +5138,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ PULSE</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4757,6 +5177,11 @@
       <c r="S17" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Pulse Rate in Orig U</t>
         </is>
       </c>
     </row>
@@ -4776,7 +5201,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ SYSBP</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4815,6 +5240,11 @@
       <c r="S18" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Systolic Blood Pressure in Orig U</t>
         </is>
       </c>
     </row>
@@ -4834,7 +5264,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ WEIGHT</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4881,6 +5311,11 @@
       <c r="S19" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Weight in Orig U</t>
         </is>
       </c>
     </row>
@@ -4900,7 +5335,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ DIABP</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4919,6 +5354,11 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Diastolic Blood Pressure Char in Std U</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5378,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ FRMSIZE</t>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4962,6 +5402,11 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>CL.SIZE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Body Frame Size - Std</t>
         </is>
       </c>
     </row>
@@ -4981,7 +5426,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ HEIGHT</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5008,6 +5453,11 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Height Char in Std U</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5477,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ PULSE</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5046,6 +5496,11 @@
       <c r="J23" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Pulse Rate Char in Std U</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5520,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ SYSBP</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5084,6 +5539,11 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Systolic Blood Pressure Char in Std U</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5563,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ WEIGHT</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5130,6 +5590,11 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Weight Char in Std U</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5614,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ BMI</t>
+          <t>WC.VS.VSTESTCD.BMI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5181,6 +5646,11 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>MT.BMISC</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>BMI (Std U)</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5670,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ DIABP</t>
+          <t>WC.VS.VSTESTCD.DIABP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5219,6 +5689,11 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Diastolic Blood Pressure Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5713,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ HEIGHT</t>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5265,6 +5740,11 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Height Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5764,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ PULSE</t>
+          <t>WC.VS.VSTESTCD.PULSE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5303,6 +5783,11 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Pulse Rate Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5807,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ SYSBP</t>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5341,6 +5826,11 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Systolic Blood Pressure Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5850,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ WEIGHT</t>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5387,6 +5877,11 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Weight Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5901,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ BMI</t>
+          <t>WC.VS.VSTESTCD.BMI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5458,6 +5953,11 @@
       <c r="S32" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>BMI Num in Std U</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5977,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ HEIGHT and DM.COUNTRY IN (CAN, MEX)</t>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5526,6 +6026,11 @@
       <c r="S33" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Height: Original Units MC</t>
         </is>
       </c>
     </row>
@@ -5545,7 +6050,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ HEIGHT and DM.COUNTRY EQ USA</t>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5589,6 +6094,11 @@
       <c r="S34" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Height: Original Units NMC</t>
         </is>
       </c>
     </row>
@@ -5608,7 +6118,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ WEIGHT and DM.COUNTRY IN (CAN, MEX)</t>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5657,6 +6167,11 @@
       <c r="S35" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Weight: Original Units MC</t>
         </is>
       </c>
     </row>
@@ -5676,7 +6191,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VSTESTCD EQ WEIGHT and DM.COUNTRY EQ USA</t>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5720,6 +6235,11 @@
       <c r="S36" t="inlineStr">
         <is>
           <t>LF.acrf</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Weight: Original Units NMC</t>
         </is>
       </c>
     </row>
@@ -10629,7 +11149,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10640,30 +11160,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Comparator</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Publishing Set</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -10672,207 +11187,769 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STD.1</t>
+          <t>WC.SUPPDM.QNAM.RACE1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SDTMIG</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>COM.STD1</t>
+          <t>RACE1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STD.2</t>
+          <t>WC.SUPPDM.QNAM.RACE2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SDTMIG</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>COM.STD2</t>
+          <t>RACE2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STD.2_1</t>
+          <t>WC.SUPPDM.QNAM.RACE3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SDTMIG-MD</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>COM.STD3</t>
+          <t>RACE3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STD.3</t>
+          <t>WC.SUPPDM.QNAM.RAND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDISC/NCI</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2011-12-09</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>COM.CT1</t>
+          <t>RAND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STD.4</t>
+          <t>WC.SUPPDM.QNAM.RANDNO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDISC/NCI</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2015-12-18</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SDTM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>COM.CT2</t>
+          <t>RANDNO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STD.5</t>
+          <t>WC.SUPPDM.QNAM.SAFETY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDISC/NCI</t>
+          <t>SUPPDM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>QNAM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DEFINE-XML</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>COM.STD5</t>
+          <t>SAFETY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMAX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AGEMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEMIN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AGEMIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.AGEU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AGEU</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.DOSE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.FCNTRY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FCNTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WC.TS.TSPARMCD.PLANSUB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PLANSUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.BMI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.DIABP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIABP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.FRMSIZE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FRMSIZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>(CAN, MEX)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HEIGHT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.HEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.PULSE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PULSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.SYSBP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SYSBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CMETRIC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>(CAN, MEX)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VSTESTCD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WEIGHT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WC.VS.VSTESTCD.WEIGHT.[DM].COUNTRY.CNMETRIC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>COM.SUBJECTDATA-JOIN-DM</t>
         </is>
       </c>
     </row>
